--- a/Procurement Progress Tracking.xlsx
+++ b/Procurement Progress Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://macest-my.sharepoint.com/personal/aqadoumi_mac-est_com/Documents/Desktop/Files/RO Plant and Collection Ground Water System/7.0 Procurement/github_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{5AEE9673-ADE1-46DE-AF4E-C6D513105EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66F2F80A-9CC8-4E5A-B0D0-DB86C2EE381E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{5AEE9673-ADE1-46DE-AF4E-C6D513105EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A3D0730-9F0A-4DC0-93E2-B74576C9BAC8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BA48F41-70E9-44C9-815A-92FFBAF3E201}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BA48F41-70E9-44C9-815A-92FFBAF3E201}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$O$472</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Breakdown for Raft found'!$A$1:$L$29</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2582,6 +2582,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2589,6 +2590,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2596,6 +2598,7 @@
       <sz val="22"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2652,6 +2655,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2659,12 +2663,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -18409,6 +18415,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
